--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,12 +130,6 @@
       <color rgb="00660000"/>
       <sz val="8"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -213,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -282,9 +276,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6388,7 +6379,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -6404,14 +6395,14 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>7%</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>5619290</v>
+        <v>7799910</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>21285</v>
+        <v>29545</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
@@ -11093,7 +11084,7 @@
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -11103,7 +11094,7 @@
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -11941,12 +11932,12 @@
 (21年-10月-11日)</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>C | 264呎 (1房)
 $839万
 $31,769/呎
-(暂停销售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -6379,7 +6379,7 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
@@ -11079,12 +11079,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -11932,12 +11932,12 @@
 (21年-10月-11日)</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>C | 264呎 (1房)
 $839万
 $31,769/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -6379,34 +6379,34 @@
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
-        <v>8387000</v>
+        <v>7926000</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>31769</v>
+        <v>30023</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>7799910</v>
+        <v>7926000</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>29545</v>
+        <v>30023</v>
       </c>
       <c r="M93" s="3" t="inlineStr">
         <is>
-          <t>120天即供付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr">
@@ -11079,7 +11079,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -11089,7 +11089,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>157</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -11932,12 +11932,12 @@
 (21年-10月-11日)</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 264呎 (1房)
-$839万
-$31,769/呎
-(在售)</t>
+$793万
+$30,023/呎
+(26年-09月-25日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -6384,7 +6384,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -11937,7 +11937,7 @@
           <t>C | 264呎 (1房)
 $793万
 $30,023/呎
-(26年-09月-25日)</t>
+(26年-10月-20日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">

--- a/files/九龙-何文田-VAU Residence.xlsx
+++ b/files/九龙-何文田-VAU Residence.xlsx
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>7657000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>27543</v>
+        <v>27643</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>7657000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>27543</v>
+        <v>27643</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>7784000</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>27603</v>
+        <v>27505</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>7784000</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>27603</v>
+        <v>27505</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1989,7 +1989,7 @@
         <v>6696000</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>24086</v>
+        <v>24173</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>6696000</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>24086</v>
+        <v>24173</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2469,7 +2469,7 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         <v>6009000</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>21615</v>
+        <v>21693</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>6009000</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>21615</v>
+        <v>21693</v>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>6325000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>22429</v>
+        <v>22350</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>6325000</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>22429</v>
+        <v>22350</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -2981,7 +2981,7 @@
         <v>5915000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>21277</v>
+        <v>21354</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>5915000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>21277</v>
+        <v>21354</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3043,7 +3043,7 @@
         <v>5911000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>20961</v>
+        <v>20887</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>5911000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>20961</v>
+        <v>20887</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3461,7 +3461,7 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -3477,7 +3477,7 @@
         <v>6637000</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>23874</v>
+        <v>23960</v>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
@@ -3488,7 +3488,7 @@
         <v>6637000</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>23874</v>
+        <v>23960</v>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>5775000</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>20773</v>
+        <v>20848</v>
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
@@ -3984,7 +3984,7 @@
         <v>5775000</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>20773</v>
+        <v>20848</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>5771000</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>20465</v>
+        <v>20392</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
         <v>5771000</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>20465</v>
+        <v>20392</v>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>6597000</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>23730</v>
+        <v>23816</v>
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>6597000</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>23730</v>
+        <v>23816</v>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>6273000</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>22245</v>
+        <v>22166</v>
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
@@ -4542,7 +4542,7 @@
         <v>6273000</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>22245</v>
+        <v>22166</v>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
@@ -4949,7 +4949,7 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>7853000</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>28248</v>
+        <v>28350</v>
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         <v>7853000</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>28248</v>
+        <v>28350</v>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
@@ -5011,7 +5011,7 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
@@ -5027,7 +5027,7 @@
         <v>6348000</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>22511</v>
+        <v>22431</v>
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         <v>6348000</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>22511</v>
+        <v>22431</v>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
@@ -5445,7 +5445,7 @@
         </is>
       </c>
       <c r="E78" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>5632000</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>20259</v>
+        <v>20332</v>
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>5632000</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>20259</v>
+        <v>20332</v>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="E79" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>5956000</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>21121</v>
+        <v>21046</v>
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>5956000</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>21121</v>
+        <v>21046</v>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
         </is>
       </c>
       <c r="E86" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>5593000</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>20119</v>
+        <v>20191</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -5968,7 +5968,7 @@
         <v>5593000</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>20119</v>
+        <v>20191</v>
       </c>
       <c r="M86" s="3" t="inlineStr">
         <is>
@@ -6003,7 +6003,7 @@
         </is>
       </c>
       <c r="E87" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
@@ -6019,7 +6019,7 @@
         <v>5938000</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>21057</v>
+        <v>20982</v>
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
@@ -6030,7 +6030,7 @@
         <v>5938000</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>21057</v>
+        <v>20982</v>
       </c>
       <c r="M87" s="3" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         </is>
       </c>
       <c r="E94" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F94" s="3" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>7535000</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>27104</v>
+        <v>27202</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>7535000</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>27104</v>
+        <v>27202</v>
       </c>
       <c r="M94" s="3" t="inlineStr">
         <is>
@@ -6499,7 +6499,7 @@
         </is>
       </c>
       <c r="E95" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F95" s="3" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>5476000</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>19418</v>
+        <v>19350</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>5476000</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>19418</v>
+        <v>19350</v>
       </c>
       <c r="M95" s="3" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -6949,7 +6949,7 @@
         <v>7346000</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>26424</v>
+        <v>26520</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -6960,7 +6960,7 @@
         <v>7346000</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>26424</v>
+        <v>26520</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="E103" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
@@ -7011,7 +7011,7 @@
         <v>7339000</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>26025</v>
+        <v>25933</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>7339000</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>26025</v>
+        <v>25933</v>
       </c>
       <c r="M103" s="3" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         </is>
       </c>
       <c r="E111" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F111" s="3" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>7309000</v>
       </c>
       <c r="I111" s="5" t="n">
-        <v>25918</v>
+        <v>25827</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         <v>7309000</v>
       </c>
       <c r="L111" s="5" t="n">
-        <v>25918</v>
+        <v>25827</v>
       </c>
       <c r="M111" s="3" t="inlineStr">
         <is>
@@ -7987,7 +7987,7 @@
         </is>
       </c>
       <c r="E119" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
@@ -8003,7 +8003,7 @@
         <v>5295000</v>
       </c>
       <c r="I119" s="5" t="n">
-        <v>18777</v>
+        <v>18710</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -8014,7 +8014,7 @@
         <v>5295000</v>
       </c>
       <c r="L119" s="5" t="n">
-        <v>18777</v>
+        <v>18710</v>
       </c>
       <c r="M119" s="3" t="inlineStr">
         <is>
@@ -8483,7 +8483,7 @@
         </is>
       </c>
       <c r="E127" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         <v>5273000</v>
       </c>
       <c r="I127" s="5" t="n">
-        <v>18699</v>
+        <v>18633</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>5273000</v>
       </c>
       <c r="L127" s="5" t="n">
-        <v>18699</v>
+        <v>18633</v>
       </c>
       <c r="M127" s="3" t="inlineStr">
         <is>
@@ -8917,7 +8917,7 @@
         </is>
       </c>
       <c r="E134" s="4" t="n">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="F134" s="3" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>6832000</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>24576</v>
+        <v>24664</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>6832000</v>
       </c>
       <c r="L134" s="5" t="n">
-        <v>24576</v>
+        <v>24664</v>
       </c>
       <c r="M134" s="3" t="inlineStr">
         <is>
@@ -10467,7 +10467,7 @@
         </is>
       </c>
       <c r="E159" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F159" s="3" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>7136000</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>25305</v>
+        <v>25216</v>
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
@@ -10494,7 +10494,7 @@
         <v>7136000</v>
       </c>
       <c r="L159" s="5" t="n">
-        <v>25305</v>
+        <v>25216</v>
       </c>
       <c r="M159" s="3" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         </is>
       </c>
       <c r="E167" s="4" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="F167" s="3" t="inlineStr">
         <is>
@@ -10979,7 +10979,7 @@
         <v>7106000</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>25199</v>
+        <v>25110</v>
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
@@ -10990,7 +10990,7 @@
         <v>7106000</v>
       </c>
       <c r="L167" s="5" t="n">
-        <v>25199</v>
+        <v>25110</v>
       </c>
       <c r="M167" s="3" t="inlineStr">
         <is>
@@ -11222,17 +11222,17 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $778万
-$27,603/呎
+$27,505/呎
 (26年-05月-05日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $766万
-$27,543/呎
+$27,643/呎
 (26年-05月-05日)</t>
         </is>
       </c>
@@ -11294,9 +11294,9 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $670万
-$24,086/呎
+$24,173/呎
 (26年-01月-09日)</t>
         </is>
       </c>
@@ -11350,17 +11350,17 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $632万
-$22,429/呎
+$22,350/呎
 (25年-11月-26日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $601万
-$21,615/呎
+$21,693/呎
 (24年-10月-18日)</t>
         </is>
       </c>
@@ -11421,17 +11421,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $591万
-$20,961/呎
+$20,887/呎
 (25年-05月-23日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $592万
-$21,277/呎
+$21,354/呎
 (24年-09月-03日)</t>
         </is>
       </c>
@@ -11500,9 +11500,9 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $664万
-$23,874/呎
+$23,960/呎
 (25年-11月-19日)</t>
         </is>
       </c>
@@ -11563,17 +11563,17 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $577万
-$20,465/呎
+$20,392/呎
 (25年-04月-09日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $578万
-$20,773/呎
+$20,848/呎
 (24年-08月-26日)</t>
         </is>
       </c>
@@ -11634,17 +11634,17 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $627万
-$22,245/呎
+$22,166/呎
 (25年-11月-25日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $660万
-$23,730/呎
+$23,816/呎
 (25年-11月-24日)</t>
         </is>
       </c>
@@ -11705,17 +11705,17 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $635万
-$22,511/呎
+$22,431/呎
 (26年-02月-24日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $785万
-$28,248/呎
+$28,350/呎
 (26年-06月-15日)</t>
         </is>
       </c>
@@ -11776,17 +11776,17 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $596万
-$21,121/呎
+$21,046/呎
 (25年-06月-30日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $563万
-$20,259/呎
+$20,332/呎
 (24年-11月-15日)</t>
         </is>
       </c>
@@ -11847,17 +11847,17 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $594万
-$21,057/呎
+$20,982/呎
 (25年-06月-27日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $559万
-$20,119/呎
+$20,191/呎
 (24年-11月-22日)</t>
         </is>
       </c>
@@ -11918,17 +11918,17 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $548万
-$19,418/呎
+$19,350/呎
 (24年-10月-24日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $754万
-$27,104/呎
+$27,202/呎
 (21年-10月-11日)</t>
         </is>
       </c>
@@ -11989,17 +11989,17 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $734万
-$26,025/呎
+$25,933/呎
 (21年-07月-09日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $735万
-$26,424/呎
+$26,520/呎
 (21年-07月-15日)</t>
         </is>
       </c>
@@ -12060,9 +12060,9 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $731万
-$25,918/呎
+$25,827/呎
 (21年-07月-13日)</t>
         </is>
       </c>
@@ -12131,9 +12131,9 @@
       </c>
       <c r="B19" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $530万
-$18,777/呎
+$18,710/呎
 (24年-08月-30日)</t>
         </is>
       </c>
@@ -12202,9 +12202,9 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $527万
-$18,699/呎
+$18,633/呎
 (24年-08月-21日)</t>
         </is>
       </c>
@@ -12281,9 +12281,9 @@
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>B | 278呎 (1房)
+          <t>B | 277呎 (1房)
 $683万
-$24,576/呎
+$24,664/呎
 (21年-07月-08日)</t>
         </is>
       </c>
@@ -12486,9 +12486,9 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $714万
-$25,305/呎
+$25,216/呎
 (21年-07月-12日)</t>
         </is>
       </c>
@@ -12557,9 +12557,9 @@
       </c>
       <c r="B25" s="22" t="inlineStr">
         <is>
-          <t>A | 282呎 (1房)
+          <t>A | 283呎 (1房)
 $711万
-$25,199/呎
+$25,110/呎
 (21年-07月-13日)</t>
         </is>
       </c>
